--- a/application/assets/excel/rekap_realisasi_anggaran.xlsx
+++ b/application/assets/excel/rekap_realisasi_anggaran.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\noval\application\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D11E3C5-0EFD-400C-9471-13EE33D3B7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E39861-1BE5-4FCD-99B0-EF16FF3C7F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E7A15CC7-3E23-4118-92B5-661F9C474EDE}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Nomor Kontrak</t>
   </si>
   <si>
-    <t>Laporan Realisasi Anggaran</t>
-  </si>
-  <si>
     <t>Tanggal Realisasi</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
   </si>
   <si>
     <t>Total Detail</t>
+  </si>
+  <si>
+    <t>Rekap Realisasi Anggaran</t>
   </si>
 </sst>
 </file>
@@ -459,7 +459,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -500,10 +500,10 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>6</v>
@@ -518,7 +518,7 @@
         <v>3</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>5</v>
